--- a/Seção 6/87.ProcV.xlsx
+++ b/Seção 6/87.ProcV.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://enelcom-my.sharepoint.com/personal/felipe_viana2_enel_com/Documents/Documentos/Faculdade/Udemy/Excell/Seção 6/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://enelcom-my.sharepoint.com/personal/felipe_viana2_enel_com/Documents/Documentos/Faculdade/Udemy/Excell/excel-data-analytics-portfolio/Seção 6/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="98" documentId="13_ncr:1_{57110A32-8596-4D1D-A959-DEBFC79F9016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D523C02-FB54-4C03-92C2-FB4CFEFDCBB9}"/>
+  <xr:revisionPtr revIDLastSave="100" documentId="13_ncr:1_{57110A32-8596-4D1D-A959-DEBFC79F9016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{820EB2F0-8A73-473B-8C6F-F0081F0D7888}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="859" firstSheet="5" activeTab="10" xr2:uid="{2E65B82F-5866-47B8-BB74-66991D6C79DA}"/>
   </bookViews>
@@ -514,6 +514,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4927,7 +4931,7 @@
         <v>75</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
@@ -4990,15 +4994,15 @@
       </c>
       <c r="G9" s="17" t="str">
         <f>$H$5&amp;F9</f>
-        <v>Nicolas Pereira1</v>
+        <v>Aline Rosa1</v>
       </c>
       <c r="H9" s="18" t="str">
         <f>IFERROR(VLOOKUP($G9,$A:$C,COLUMN(B1),0),"-")</f>
-        <v>Nicolas Pereira</v>
+        <v>Aline Rosa</v>
       </c>
       <c r="I9" s="18" t="str">
         <f>IFERROR(VLOOKUP($G9,$A:$C,COLUMN(C1),0),"-")</f>
-        <v>Camisa Masculina</v>
+        <v>Bota Masculina</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="21" x14ac:dyDescent="0.5">
@@ -5021,15 +5025,15 @@
       </c>
       <c r="G10" s="17" t="str">
         <f t="shared" ref="G10:G17" si="1">$H$5&amp;F10</f>
-        <v>Nicolas Pereira2</v>
+        <v>Aline Rosa2</v>
       </c>
       <c r="H10" s="18" t="str">
         <f t="shared" ref="H10:I10" si="2">IFERROR(VLOOKUP($G10,$A:$C,COLUMN(B2),0),"-")</f>
-        <v>Nicolas Pereira</v>
+        <v>Aline Rosa</v>
       </c>
       <c r="I10" s="18" t="str">
         <f t="shared" si="2"/>
-        <v>Kit de Pinceis de Maquiagem</v>
+        <v>Bota Masculina</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="21" x14ac:dyDescent="0.5">
@@ -5052,15 +5056,15 @@
       </c>
       <c r="G11" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Nicolas Pereira3</v>
+        <v>Aline Rosa3</v>
       </c>
       <c r="H11" s="18" t="str">
         <f t="shared" ref="H11:I11" si="3">IFERROR(VLOOKUP($G11,$A:$C,COLUMN(B3),0),"-")</f>
-        <v>Nicolas Pereira</v>
+        <v>Aline Rosa</v>
       </c>
       <c r="I11" s="18" t="str">
         <f t="shared" si="3"/>
-        <v>Sapato Social</v>
+        <v>Bermuda Masculino</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="21" x14ac:dyDescent="0.5">
@@ -5083,15 +5087,15 @@
       </c>
       <c r="G12" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Nicolas Pereira4</v>
+        <v>Aline Rosa4</v>
       </c>
       <c r="H12" s="18" t="str">
         <f t="shared" ref="H12:I12" si="4">IFERROR(VLOOKUP($G12,$A:$C,COLUMN(B4),0),"-")</f>
-        <v>Nicolas Pereira</v>
+        <v>Aline Rosa</v>
       </c>
       <c r="I12" s="18" t="str">
         <f t="shared" si="4"/>
-        <v>Bermuda Masculino</v>
+        <v>Camisa Masculina</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="21" x14ac:dyDescent="0.5">
@@ -5114,15 +5118,15 @@
       </c>
       <c r="G13" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Nicolas Pereira5</v>
+        <v>Aline Rosa5</v>
       </c>
       <c r="H13" s="18" t="str">
         <f t="shared" ref="H13:I13" si="5">IFERROR(VLOOKUP($G13,$A:$C,COLUMN(B5),0),"-")</f>
-        <v>Nicolas Pereira</v>
+        <v>Aline Rosa</v>
       </c>
       <c r="I13" s="18" t="str">
         <f t="shared" si="5"/>
-        <v>Kit de Pinceis de Maquiagem</v>
+        <v>Chinelo</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="21" x14ac:dyDescent="0.5">
@@ -5145,15 +5149,15 @@
       </c>
       <c r="G14" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Nicolas Pereira6</v>
+        <v>Aline Rosa6</v>
       </c>
       <c r="H14" s="18" t="str">
         <f t="shared" ref="H14:I14" si="6">IFERROR(VLOOKUP($G14,$A:$C,COLUMN(B6),0),"-")</f>
-        <v>Nicolas Pereira</v>
+        <v>-</v>
       </c>
       <c r="I14" s="18" t="str">
         <f t="shared" si="6"/>
-        <v>Camisa Térmica</v>
+        <v>-</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="21" x14ac:dyDescent="0.5">
@@ -5176,7 +5180,7 @@
       </c>
       <c r="G15" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Nicolas Pereira7</v>
+        <v>Aline Rosa7</v>
       </c>
       <c r="H15" s="18" t="str">
         <f t="shared" ref="H15:I15" si="7">IFERROR(VLOOKUP($G15,$A:$C,COLUMN(B7),0),"-")</f>
@@ -5207,7 +5211,7 @@
       </c>
       <c r="G16" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Nicolas Pereira8</v>
+        <v>Aline Rosa8</v>
       </c>
       <c r="H16" s="18" t="str">
         <f t="shared" ref="H16:I16" si="8">IFERROR(VLOOKUP($G16,$A:$C,COLUMN(B8),0),"-")</f>
@@ -5238,7 +5242,7 @@
       </c>
       <c r="G17" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>Nicolas Pereira9</v>
+        <v>Aline Rosa9</v>
       </c>
       <c r="H17" s="18" t="str">
         <f t="shared" ref="H17:I17" si="9">IFERROR(VLOOKUP($G17,$A:$C,COLUMN(B9),0),"-")</f>
@@ -5705,7 +5709,7 @@
   </headerFooter>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{88E70709-03ED-4C33-A805-2624A835F3DC}">
           <x14:formula1>
             <xm:f>Dados!$A$2:$A$9</xm:f>
@@ -5719,21 +5723,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7FBF0B9CEACA34A981A7F46EA19F3F9" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4f484b9883a95de778a6ce333a5c9fbe">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="fd550b8b-0dd7-4de3-a8e6-af527f15a8ac" xmlns:ns4="45cbc027-4fdb-4325-ba4c-14e20f088a7f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="918a0d7af8be30ff2596a9f3dd2488fd" ns3:_="" ns4:_="">
     <xsd:import namespace="fd550b8b-0dd7-4de3-a8e6-af527f15a8ac"/>
@@ -5930,10 +5919,36 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8981F02B-5252-40A8-85C9-6E028D5DC5D2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DF8C6D0-BDB8-4D22-A8A4-DEAEBC30EDA1}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="fd550b8b-0dd7-4de3-a8e6-af527f15a8ac"/>
+    <ds:schemaRef ds:uri="45cbc027-4fdb-4325-ba4c-14e20f088a7f"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5956,20 +5971,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DF8C6D0-BDB8-4D22-A8A4-DEAEBC30EDA1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8981F02B-5252-40A8-85C9-6E028D5DC5D2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="fd550b8b-0dd7-4de3-a8e6-af527f15a8ac"/>
-    <ds:schemaRef ds:uri="45cbc027-4fdb-4325-ba4c-14e20f088a7f"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>